--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223489</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131223515</v>
       </c>
       <c r="B16" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131223489</v>
+        <v>131223149</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>773011</v>
+        <v>772974</v>
       </c>
       <c r="R2" t="n">
-        <v>7122664</v>
+        <v>7122563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,13 +756,17 @@
           <t>2026-02-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131223149</v>
+        <v>131223060</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772974</v>
+        <v>772981</v>
       </c>
       <c r="R3" t="n">
-        <v>7122563</v>
+        <v>7122639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131223060</v>
+        <v>131223489</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,31 +906,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772981</v>
+        <v>773011</v>
       </c>
       <c r="R4" t="n">
-        <v>7122639</v>
+        <v>7122664</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,17 +975,13 @@
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>131223226</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131222842</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131223089</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>131222927</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>131223447</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>131223461</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>131223199</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>131223021</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>131223133</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>131222888</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131223215</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131223515</v>
       </c>
       <c r="B16" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131223012</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>131223365</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131223149</v>
+        <v>131223489</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772974</v>
+        <v>773011</v>
       </c>
       <c r="R2" t="n">
-        <v>7122563</v>
+        <v>7122664</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +755,13 @@
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131223060</v>
+        <v>131223149</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772981</v>
+        <v>772974</v>
       </c>
       <c r="R3" t="n">
-        <v>7122639</v>
+        <v>7122563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131223489</v>
+        <v>131223060</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,30 +901,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>773011</v>
+        <v>772981</v>
       </c>
       <c r="R4" t="n">
-        <v>7122664</v>
+        <v>7122639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,13 +971,17 @@
           <t>2026-02-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>131223226</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131222842</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131223089</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>131222927</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>131223447</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>131223461</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>131223199</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>131223021</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>131223133</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>131222888</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131223215</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131223515</v>
       </c>
       <c r="B16" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131223012</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>131223365</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131223489</v>
+        <v>131223149</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>773011</v>
+        <v>772974</v>
       </c>
       <c r="R2" t="n">
-        <v>7122664</v>
+        <v>7122563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,13 +756,17 @@
           <t>2026-02-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131223149</v>
+        <v>131223060</v>
       </c>
       <c r="B3" t="n">
         <v>57887</v>
@@ -823,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772974</v>
+        <v>772981</v>
       </c>
       <c r="R3" t="n">
-        <v>7122563</v>
+        <v>7122639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131223060</v>
+        <v>131223489</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,31 +906,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772981</v>
+        <v>773011</v>
       </c>
       <c r="R4" t="n">
-        <v>7122639</v>
+        <v>7122664</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,17 +975,13 @@
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223149</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131223060</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>131223489</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131223226</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131222842</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131223089</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>131222927</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>131223447</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>131223461</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>131223199</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>131223021</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>131223133</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>131222888</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131223215</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131223515</v>
       </c>
       <c r="B16" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131223012</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>131223365</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131223149</v>
+        <v>131223489</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772974</v>
+        <v>773011</v>
       </c>
       <c r="R2" t="n">
-        <v>7122563</v>
+        <v>7122664</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +755,13 @@
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131223060</v>
+        <v>131223149</v>
       </c>
       <c r="B3" t="n">
         <v>57888</v>
@@ -828,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772981</v>
+        <v>772974</v>
       </c>
       <c r="R3" t="n">
-        <v>7122639</v>
+        <v>7122563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131223489</v>
+        <v>131223060</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,30 +901,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>773011</v>
+        <v>772981</v>
       </c>
       <c r="R4" t="n">
-        <v>7122664</v>
+        <v>7122639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,13 +971,17 @@
           <t>2026-02-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131223489</v>
+        <v>131223149</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>773011</v>
+        <v>772974</v>
       </c>
       <c r="R2" t="n">
-        <v>7122664</v>
+        <v>7122563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,13 +756,17 @@
           <t>2026-02-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131223149</v>
+        <v>131223060</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772974</v>
+        <v>772981</v>
       </c>
       <c r="R3" t="n">
-        <v>7122563</v>
+        <v>7122639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131223060</v>
+        <v>131223489</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,31 +906,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772981</v>
+        <v>773011</v>
       </c>
       <c r="R4" t="n">
-        <v>7122639</v>
+        <v>7122664</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,17 +975,13 @@
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>131223226</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131222842</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131223089</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>131222927</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>131223447</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>131223461</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>131223199</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>131223021</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>131223133</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>131222888</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131223215</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131223515</v>
       </c>
       <c r="B16" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131223012</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>131223365</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131223149</v>
+        <v>131223489</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772974</v>
+        <v>773011</v>
       </c>
       <c r="R2" t="n">
-        <v>7122563</v>
+        <v>7122664</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +755,13 @@
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131223060</v>
+        <v>131223149</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772981</v>
+        <v>772974</v>
       </c>
       <c r="R3" t="n">
-        <v>7122639</v>
+        <v>7122563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131223489</v>
+        <v>131223060</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,30 +901,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>773011</v>
+        <v>772981</v>
       </c>
       <c r="R4" t="n">
-        <v>7122664</v>
+        <v>7122639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,13 +971,17 @@
           <t>2026-02-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>131223226</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131222842</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131223089</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>131222927</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>131223447</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>131223461</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>131223199</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>131223021</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>131223133</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131222888</v>
+        <v>131223215</v>
       </c>
       <c r="B14" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>772928</v>
+        <v>772982</v>
       </c>
       <c r="R14" t="n">
-        <v>7122645</v>
+        <v>7122561</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131223215</v>
+        <v>131222888</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>772982</v>
+        <v>772928</v>
       </c>
       <c r="R15" t="n">
-        <v>7122561</v>
+        <v>7122645</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>färska ringhack på två granar</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,7 +2213,7 @@
         <v>131223515</v>
       </c>
       <c r="B16" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131223012</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>131223365</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223489</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131223149</v>
       </c>
       <c r="B3" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131223060</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131223226</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131222842</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131223089</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>131222927</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>131223447</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>131223461</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>131223199</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>131223021</v>
       </c>
       <c r="B12" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>131223133</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131223215</v>
+        <v>131222888</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>772982</v>
+        <v>772928</v>
       </c>
       <c r="R14" t="n">
-        <v>7122561</v>
+        <v>7122645</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska ringhack på två granar</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131222888</v>
+        <v>131223215</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>772928</v>
+        <v>772982</v>
       </c>
       <c r="R15" t="n">
-        <v>7122645</v>
+        <v>7122561</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,7 +2213,7 @@
         <v>131223515</v>
       </c>
       <c r="B16" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131223012</v>
       </c>
       <c r="B17" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>131223365</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131223489</v>
+        <v>131223149</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>773011</v>
+        <v>772974</v>
       </c>
       <c r="R2" t="n">
-        <v>7122664</v>
+        <v>7122563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,13 +756,17 @@
           <t>2026-02-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131223149</v>
+        <v>131223060</v>
       </c>
       <c r="B3" t="n">
         <v>57898</v>
@@ -823,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772974</v>
+        <v>772981</v>
       </c>
       <c r="R3" t="n">
-        <v>7122563</v>
+        <v>7122639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131223060</v>
+        <v>131223489</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,31 +906,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772981</v>
+        <v>773011</v>
       </c>
       <c r="R4" t="n">
-        <v>7122639</v>
+        <v>7122664</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,17 +975,13 @@
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131223149</v>
+        <v>131223489</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772974</v>
+        <v>773011</v>
       </c>
       <c r="R2" t="n">
-        <v>7122563</v>
+        <v>7122664</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +755,13 @@
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131223060</v>
+        <v>131223149</v>
       </c>
       <c r="B3" t="n">
         <v>57898</v>
@@ -828,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772981</v>
+        <v>772974</v>
       </c>
       <c r="R3" t="n">
-        <v>7122639</v>
+        <v>7122563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131223489</v>
+        <v>131223060</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,30 +901,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>773011</v>
+        <v>772981</v>
       </c>
       <c r="R4" t="n">
-        <v>7122664</v>
+        <v>7122639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,13 +971,17 @@
           <t>2026-02-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223489</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131223149</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131223060</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131223226</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131222842</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131223089</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>131222927</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>131223447</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>131223461</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>131223199</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>131223021</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>131223133</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>131222888</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131223215</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131223515</v>
       </c>
       <c r="B16" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131223012</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>131223365</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 2639-2026 artfynd.xlsx
+++ b/artfynd/A 2639-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223515</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223489</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131222842</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131222888</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131222927</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223012</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223021</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223060</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223089</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223133</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1872,6 +1927,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223149</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1982,6 +2042,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223174</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2092,6 +2157,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223199</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2202,6 +2272,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223215</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2312,6 +2387,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223226</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2422,6 +2502,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223248</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2532,6 +2617,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223268</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2642,6 +2732,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223274</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2752,6 +2847,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223365</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2862,6 +2962,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223421</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2972,6 +3077,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223447</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3082,8 +3192,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223461</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>